--- a/output/pdf_financials_xlsx/TCF.xlsx
+++ b/output/pdf_financials_xlsx/TCF.xlsx
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>20.278827</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>15.096374</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>8.107494000000001</v>
       </c>
     </row>
     <row r="11">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019179</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.053386</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.225997</v>
       </c>
     </row>
     <row r="13">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.816484</v>
+        <v>1.797305</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.681589</v>
+        <v>-6.734975</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-52.713569</v>
+        <v>-52.939566</v>
       </c>
     </row>
     <row r="28">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.992248</v>
+        <v>1.973069</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.594181</v>
+        <v>-6.647567</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-52.64878</v>
+        <v>-52.874777</v>
       </c>
     </row>
     <row r="30">
@@ -3446,16 +3446,16 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004121</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.085271</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022921</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014449</v>
       </c>
     </row>
     <row r="125">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004121</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.085271</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022921</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014449</v>
       </c>
     </row>
     <row r="126">
@@ -8281,7 +8281,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -12051,7 +12055,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12133,7 +12137,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCF.xlsx
+++ b/output/pdf_financials_xlsx/TCF.xlsx
@@ -2087,22 +2087,20 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.113616</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.886324</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.07707799999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.240462</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.371047</v>
       </c>
     </row>
     <row r="68">
@@ -2165,10 +2163,10 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.027693</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.008592000000000001</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -2189,10 +2187,10 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.549424</v>
+        <v>0.577117</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.46445</v>
+        <v>3.473042</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>5.361978</v>
@@ -2285,10 +2283,10 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.012116</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.265127</v>
+        <v>0.256535</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>10.375349</v>
@@ -2405,10 +2403,10 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>-0.08094962998912812</v>
+        <v>-0.08502979049046938</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.1559679806552794</v>
+        <v>0.1563547886305107</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>1072395.6</v>
@@ -6431,7 +6429,11 @@
           <t>Lease liabilities 11 122,058 4,552</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -8993,7 +8995,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
